--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E351"/>
+  <dimension ref="A1:E355"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -9228,6 +9228,106 @@
         </is>
       </c>
     </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B352" s="3" t="n">
+        <v>18.41</v>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>2026-09-06T11:33:41.006Z</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>2026-09-06 11:39:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B353" s="3" t="n">
+        <v>95.84999999999999</v>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>2026-09-06T11:38:43.300Z</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>2026-09-06 11:39:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B354" s="3" t="n">
+        <v>24.02</v>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>2026-09-05T00:26:10.258Z</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>2026-09-06 11:39:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B355" s="3" t="n">
+        <v>84.18000000000001</v>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>2026-09-05T00:26:42.864Z</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>2026-09-06 11:39:42</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E355"/>
+  <dimension ref="A1:E359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -9328,6 +9328,106 @@
         </is>
       </c>
     </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B356" s="3" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>2026-09-07T13:22:06.116Z</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:31:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B357" s="3" t="n">
+        <v>97.08</v>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>2026-09-07T13:30:27.099Z</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:31:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B358" s="3" t="n">
+        <v>24.02</v>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>2026-09-05T00:26:10.258Z</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:31:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B359" s="3" t="n">
+        <v>84.18000000000001</v>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>2026-09-05T00:26:42.864Z</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>2026-09-07 13:31:03</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E359"/>
+  <dimension ref="A1:E363"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -9428,6 +9428,106 @@
         </is>
       </c>
     </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B360" s="3" t="n">
+        <v>18.95</v>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>2026-09-08T12:08:29.369Z</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>2026-09-08 12:08:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B361" s="3" t="n">
+        <v>98.66</v>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>2026-09-08T12:07:32.310Z</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>2026-09-08 12:08:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B362" s="3" t="n">
+        <v>24.02</v>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>2026-09-05T00:26:10.258Z</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>2026-09-08 12:08:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B363" s="3" t="n">
+        <v>84.73999999999999</v>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>2026-09-08T00:06:25.650Z</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>2026-09-08 12:08:58</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E363"/>
+  <dimension ref="A1:E367"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -9528,6 +9528,106 @@
         </is>
       </c>
     </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B364" s="3" t="n">
+        <v>19.677</v>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>2026-09-09T12:16:24.514Z</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>2026-09-09 12:20:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B365" s="3" t="n">
+        <v>100.86</v>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>2026-09-09T12:20:38.111Z</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>2026-09-09 12:20:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B366" s="3" t="n">
+        <v>24.38</v>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>2026-09-09T00:01:37.554Z</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>2026-09-09 12:20:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B367" s="3" t="n">
+        <v>85.42</v>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>2026-09-09T00:02:09.778Z</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>2026-09-09 12:20:40</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E367"/>
+  <dimension ref="A1:E371"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -9628,6 +9628,106 @@
         </is>
       </c>
     </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B368" s="3" t="n">
+        <v>20.69</v>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>2026-09-10T12:10:33.832Z</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>2026-09-10 12:14:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B369" s="3" t="n">
+        <v>103.27</v>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>2026-09-10T12:13:16.448Z</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>2026-09-10 12:14:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B370" s="3" t="n">
+        <v>24.68</v>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>2026-09-10T00:01:14.944Z</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>2026-09-10 12:14:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B371" s="3" t="n">
+        <v>85.56999999999999</v>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>2026-09-10T00:01:54.096Z</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>2026-09-10 12:14:26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E371"/>
+  <dimension ref="A1:E375"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -9728,6 +9728,106 @@
         </is>
       </c>
     </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B372" s="3" t="n">
+        <v>20.53</v>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>2026-09-11T12:10:34.446Z</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>2026-09-11 12:12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B373" s="3" t="n">
+        <v>104.11</v>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>2026-09-11T12:11:14.986Z</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>2026-09-11 12:12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B374" s="3" t="n">
+        <v>24.81</v>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>2026-09-11T00:06:20.155Z</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>2026-09-11 12:12:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B375" s="3" t="n">
+        <v>85.81999999999999</v>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>2026-09-11T00:06:49.122Z</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>2026-09-11 12:12:30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E375"/>
+  <dimension ref="A1:E379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -9828,6 +9828,106 @@
         </is>
       </c>
     </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B376" s="3" t="n">
+        <v>20.33</v>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>2026-09-12T10:45:34.898Z</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>2026-09-12 11:36:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B377" s="3" t="n">
+        <v>104.32</v>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>2026-09-12T10:38:21.684Z</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>2026-09-12 11:36:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B378" s="3" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>2026-09-12T00:01:07.683Z</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>2026-09-12 11:36:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B379" s="3" t="n">
+        <v>85.52</v>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>2026-09-12T00:01:41.092Z</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>2026-09-12 11:36:43</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E379"/>
+  <dimension ref="A1:E383"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -9928,6 +9928,106 @@
         </is>
       </c>
     </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B380" s="3" t="n">
+        <v>19.826</v>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>2026-09-13T12:40:43.210Z</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>2026-09-13 12:43:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B381" s="3" t="n">
+        <v>104.47</v>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>2026-09-13T12:42:50.199Z</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>2026-09-13 12:43:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B382" s="3" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>2026-09-12T00:01:07.683Z</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>2026-09-13 12:43:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B383" s="3" t="n">
+        <v>85.52</v>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>2026-09-12T00:01:41.092Z</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>2026-09-13 12:43:53</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E383"/>
+  <dimension ref="A1:E387"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -10028,6 +10028,106 @@
         </is>
       </c>
     </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B384" s="3" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>2026-09-14T13:58:25.036Z</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:05:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B385" s="3" t="n">
+        <v>108.89</v>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>2026-09-14T14:04:24.779Z</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:05:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B386" s="3" t="n">
+        <v>24.88</v>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>2026-09-12T00:01:07.683Z</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:05:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B387" s="3" t="n">
+        <v>85.52</v>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>2026-09-12T00:01:41.092Z</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>2026-09-14 14:05:06</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E387"/>
+  <dimension ref="A1:E391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -10128,6 +10128,106 @@
         </is>
       </c>
     </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B388" s="3" t="n">
+        <v>19.617</v>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>2026-09-15T12:40:33.234Z</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:41:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B389" s="3" t="n">
+        <v>106.71</v>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>2026-09-15T12:40:28.987Z</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:41:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B390" s="3" t="n">
+        <v>25.06</v>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>2026-09-15T00:00:55.434Z</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:41:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B391" s="3" t="n">
+        <v>87.98999999999999</v>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>2026-09-15T00:01:34.595Z</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>2026-09-15 12:41:38</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E391"/>
+  <dimension ref="A1:E395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -10228,6 +10228,106 @@
         </is>
       </c>
     </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B392" s="3" t="n">
+        <v>20.25</v>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>2026-09-16T12:35:48.005Z</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:36:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B393" s="3" t="n">
+        <v>107.31</v>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>2026-09-16T12:36:17.219Z</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:36:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B394" s="3" t="n">
+        <v>27.76</v>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>2026-09-16T00:01:13.737Z</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:36:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B395" s="3" t="n">
+        <v>85.61</v>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>2026-09-16T00:01:58.738Z</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>2026-09-16 12:36:39</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E395"/>
+  <dimension ref="A1:E399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -10328,6 +10328,106 @@
         </is>
       </c>
     </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B396" s="3" t="n">
+        <v>19.49</v>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>2026-09-17T12:34:12.414Z</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>2026-09-17 12:36:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B397" s="3" t="n">
+        <v>101.89</v>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>2026-09-17T12:35:26.993Z</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>2026-09-17 12:36:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B398" s="3" t="n">
+        <v>27.22</v>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>2026-09-17T00:01:30.152Z</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>2026-09-17 12:36:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B399" s="3" t="n">
+        <v>84.73999999999999</v>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>2026-09-17T00:01:59.928Z</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>2026-09-17 12:36:02</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E399"/>
+  <dimension ref="A1:E403"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -10428,6 +10428,106 @@
         </is>
       </c>
     </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B400" s="3" t="n">
+        <v>19.72</v>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:10:24.144Z</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>2026-09-18 12:14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B401" s="3" t="n">
+        <v>103.44</v>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>2026-09-18T12:13:25.859Z</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>2026-09-18 12:14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B402" s="3" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>2026-09-18T00:00:51.785Z</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>2026-09-18 12:14:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B403" s="3" t="n">
+        <v>86.03</v>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>2026-09-18T00:01:22.934Z</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>2026-09-18 12:14:15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E403"/>
+  <dimension ref="A1:E407"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -10528,6 +10528,106 @@
         </is>
       </c>
     </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B404" s="3" t="n">
+        <v>20.03</v>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>2026-09-19T11:20:40.166Z</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>2026-09-19 11:56:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B405" s="3" t="n">
+        <v>103.37</v>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>2026-09-19T11:38:42.309Z</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>2026-09-19 11:56:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B406" s="3" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>2026-09-19T00:01:05.565Z</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>2026-09-19 11:56:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B407" s="3" t="n">
+        <v>86.89</v>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>2026-09-19T00:01:35.695Z</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>2026-09-19 11:56:01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E407"/>
+  <dimension ref="A1:E411"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -10628,6 +10628,106 @@
         </is>
       </c>
     </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B408" s="3" t="n">
+        <v>19.816</v>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>2026-09-20T12:15:28.277Z</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>2026-09-20 12:23:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B409" s="3" t="n">
+        <v>103.37</v>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>2026-09-20T12:11:35.508Z</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>2026-09-20 12:23:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B410" s="3" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>2026-09-19T00:01:05.565Z</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>2026-09-20 12:23:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B411" s="3" t="n">
+        <v>86.89</v>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>2026-09-19T00:01:35.695Z</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>2026-09-20 12:23:41</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E411"/>
+  <dimension ref="A1:E415"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -10728,6 +10728,106 @@
         </is>
       </c>
     </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B412" s="3" t="n">
+        <v>18.47</v>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>2026-09-21T14:10:22.088Z</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>2026-09-21 14:11:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B413" s="3" t="n">
+        <v>100.74</v>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>2026-09-21T14:07:15.422Z</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>2026-09-21 14:11:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B414" s="3" t="n">
+        <v>27.51</v>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>2026-09-19T00:01:05.565Z</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>2026-09-21 14:11:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B415" s="3" t="n">
+        <v>86.89</v>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>2026-09-19T00:01:35.695Z</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>2026-09-21 14:11:08</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E415"/>
+  <dimension ref="A1:E419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -10828,6 +10828,106 @@
         </is>
       </c>
     </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B416" s="3" t="n">
+        <v>17.87</v>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:34:43.078Z</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>2026-09-22 12:37:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B417" s="3" t="n">
+        <v>98.63</v>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>2026-09-22T12:37:18.455Z</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>2026-09-22 12:37:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B418" s="3" t="n">
+        <v>25.99</v>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:01:13.465Z</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>2026-09-22 12:37:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B419" s="3" t="n">
+        <v>86.59</v>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>2026-09-22T00:01:47.049Z</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>2026-09-22 12:37:44</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E419"/>
+  <dimension ref="A1:E423"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -10928,6 +10928,106 @@
         </is>
       </c>
     </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B420" s="3" t="n">
+        <v>18.49</v>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>2026-09-23T12:44:50.208Z</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:45:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B421" s="3" t="n">
+        <v>100.23</v>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>2026-09-23T12:43:18.772Z</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:45:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B422" s="3" t="n">
+        <v>26.05</v>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>2026-09-23T00:01:12.473Z</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:45:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B423" s="3" t="n">
+        <v>86.73</v>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>2026-09-23T00:01:50.730Z</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>2026-09-23 12:45:42</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E423"/>
+  <dimension ref="A1:E427"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -11028,6 +11028,106 @@
         </is>
       </c>
     </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B424" s="3" t="n">
+        <v>18.594</v>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>2026-09-24T12:40:12.770Z</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>2026-09-24 12:43:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B425" s="3" t="n">
+        <v>105.19</v>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>2026-09-24T12:43:25.555Z</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>2026-09-24 12:43:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B426" s="3" t="n">
+        <v>25.72</v>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>2026-09-24T00:01:12.297Z</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>2026-09-24 12:43:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B427" s="3" t="n">
+        <v>86.01000000000001</v>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>2026-09-24T00:01:48.148Z</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>2026-09-24 12:43:54</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E427"/>
+  <dimension ref="A1:E431"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -11128,6 +11128,106 @@
         </is>
       </c>
     </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B428" s="3" t="n">
+        <v>18.04</v>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:46:28.670Z</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:46:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B429" s="3" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>2026-09-25T12:46:27.853Z</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:47:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B430" s="3" t="n">
+        <v>26.38</v>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>2026-09-25T00:06:00.342Z</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:47:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B431" s="3" t="n">
+        <v>86.95999999999999</v>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>2026-09-25T00:06:31.335Z</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>2026-09-25 12:47:01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E431"/>
+  <dimension ref="A1:E435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -11228,6 +11228,106 @@
         </is>
       </c>
     </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B432" s="3" t="n">
+        <v>17.98</v>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>2026-09-26T11:20:29.707Z</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>2026-09-26 12:14:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B433" s="3" t="n">
+        <v>104.45</v>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>2026-09-26T12:06:46.111Z</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>2026-09-26 12:14:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B434" s="3" t="n">
+        <v>25.81</v>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>2026-09-26T00:01:06.279Z</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>2026-09-26 12:14:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B435" s="3" t="n">
+        <v>86.78</v>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>2026-09-26T00:01:39.387Z</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>2026-09-26 12:14:51</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E435"/>
+  <dimension ref="A1:E439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -11328,6 +11328,106 @@
         </is>
       </c>
     </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B436" s="3" t="n">
+        <v>17.98</v>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>2026-09-27T12:45:54.427Z</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>2026-09-27 13:03:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B437" s="3" t="n">
+        <v>104.38</v>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>2026-09-27T12:51:43.386Z</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>2026-09-27 13:03:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B438" s="3" t="n">
+        <v>25.81</v>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>2026-09-26T00:01:06.279Z</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>2026-09-27 13:03:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B439" s="3" t="n">
+        <v>86.78</v>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>2026-09-26T00:01:39.387Z</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>2026-09-27 13:03:09</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E439"/>
+  <dimension ref="A1:E443"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -11428,6 +11428,106 @@
         </is>
       </c>
     </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B440" s="3" t="n">
+        <v>18.51</v>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>2026-09-28T15:22:22.923Z</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:30:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B441" s="3" t="n">
+        <v>107.52</v>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>2026-09-28T15:28:12.495Z</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:30:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B442" s="3" t="n">
+        <v>25.81</v>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>2026-09-26T00:01:06.279Z</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:30:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B443" s="3" t="n">
+        <v>86.78</v>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>2026-09-26T00:01:39.387Z</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>2026-09-28 15:30:10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E443"/>
+  <dimension ref="A1:E447"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -11528,6 +11528,106 @@
         </is>
       </c>
     </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B444" s="3" t="n">
+        <v>17.56</v>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>2026-09-29T13:46:08.194Z</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:05:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B445" s="3" t="n">
+        <v>103.79</v>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>2026-09-29T14:04:20.956Z</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:05:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B446" s="3" t="n">
+        <v>26.08</v>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>2026-09-29T00:01:02.993Z</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:05:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B447" s="3" t="n">
+        <v>86.17</v>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>2026-09-29T00:01:33.484Z</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>2026-09-29 14:05:04</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E447"/>
+  <dimension ref="A1:E451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -11628,6 +11628,106 @@
         </is>
       </c>
     </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B448" s="3" t="n">
+        <v>18.074</v>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>2026-09-30T13:40:30.591Z</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:45:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B449" s="3" t="n">
+        <v>103.61</v>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>2026-09-30T13:45:11.776Z</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:45:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B450" s="3" t="n">
+        <v>25.43</v>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>2026-09-30T00:01:04.187Z</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:45:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B451" s="3" t="n">
+        <v>85.95</v>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>2026-09-30T00:01:34.959Z</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:45:30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E451"/>
+  <dimension ref="A1:E455"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -11728,6 +11728,106 @@
         </is>
       </c>
     </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B452" s="3" t="n">
+        <v>18.641</v>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>2026-10-01T14:16:10.176Z</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:28:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B453" s="3" t="n">
+        <v>101.13</v>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>2026-10-01T14:28:22.141Z</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:28:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B454" s="3" t="n">
+        <v>25.74</v>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>2026-10-01T00:01:00.034Z</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:28:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B455" s="3" t="n">
+        <v>85.09</v>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>2026-10-01T00:01:29.592Z</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>2026-10-01 14:28:57</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E455"/>
+  <dimension ref="A1:E459"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -11828,6 +11828,106 @@
         </is>
       </c>
     </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B456" s="3" t="n">
+        <v>18.61</v>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>2026-10-02T13:46:07.434Z</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>2026-10-02 13:52:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B457" s="3" t="n">
+        <v>99.53</v>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>2026-10-02T13:52:20.280Z</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>2026-10-02 13:52:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B458" s="3" t="n">
+        <v>25.78</v>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>2026-10-02T00:01:15.727Z</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>2026-10-02 13:52:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B459" s="3" t="n">
+        <v>85.64</v>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>2026-10-02T00:01:48.153Z</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>2026-10-02 13:52:48</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E459"/>
+  <dimension ref="A1:E463"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -11928,6 +11928,106 @@
         </is>
       </c>
     </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B460" s="3" t="n">
+        <v>18.81</v>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>2026-10-03T12:16:02.874Z</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:35:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B461" s="3" t="n">
+        <v>102.61</v>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>2026-10-03T12:26:22.988Z</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:35:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B462" s="3" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>2026-10-03T00:16:17.787Z</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:35:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B463" s="3" t="n">
+        <v>84.42</v>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>2026-10-03T00:16:43.534Z</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:35:08</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E463"/>
+  <dimension ref="A1:E467"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -12028,6 +12028,106 @@
         </is>
       </c>
     </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B464" s="3" t="n">
+        <v>19.18</v>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>2026-10-04T12:45:57.168Z</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>2026-10-04 13:12:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B465" s="3" t="n">
+        <v>102.61</v>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>2026-10-04T13:01:19.984Z</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>2026-10-04 13:12:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B466" s="3" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>2026-10-03T00:16:17.787Z</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>2026-10-04 13:12:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B467" s="3" t="n">
+        <v>84.42</v>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>2026-10-03T00:16:43.534Z</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>2026-10-04 13:12:25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E467"/>
+  <dimension ref="A1:E471"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -12128,6 +12128,106 @@
         </is>
       </c>
     </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B468" s="3" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>2026-10-05T15:58:18.606Z</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>2026-10-05 16:02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B469" s="3" t="n">
+        <v>101.53</v>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>2026-10-05T16:01:24.732Z</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>2026-10-05 16:02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B470" s="3" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>2026-10-03T00:16:17.787Z</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>2026-10-05 16:02:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B471" s="3" t="n">
+        <v>84.42</v>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>2026-10-03T00:16:43.534Z</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>2026-10-05 16:02:15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E471"/>
+  <dimension ref="A1:E475"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -12228,6 +12228,106 @@
         </is>
       </c>
     </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B472" s="3" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>2026-10-06T14:10:22.170Z</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>2026-10-06 14:12:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B473" s="3" t="n">
+        <v>98.3</v>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>2026-10-06T14:11:06.899Z</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>2026-10-06 14:12:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B474" s="3" t="n">
+        <v>25.71</v>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>2026-10-06T00:06:08.717Z</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>2026-10-06 14:12:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B475" s="3" t="n">
+        <v>83.87</v>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>2026-10-06T00:06:33.905Z</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>2026-10-06 14:12:38</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E475"/>
+  <dimension ref="A1:E479"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -12328,6 +12328,106 @@
         </is>
       </c>
     </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B476" s="3" t="n">
+        <v>19.07</v>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>2026-10-07T14:22:15.894Z</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:31:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B477" s="3" t="n">
+        <v>102.02</v>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>2026-10-07T14:31:31.930Z</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:31:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B478" s="3" t="n">
+        <v>25.88</v>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>2026-10-07T00:01:22.318Z</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:31:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B479" s="3" t="n">
+        <v>84.78</v>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>2026-10-07T00:01:49.531Z</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>2026-10-07 14:31:38</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E479"/>
+  <dimension ref="A1:E483"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -12428,6 +12428,106 @@
         </is>
       </c>
     </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B480" s="3" t="n">
+        <v>19.56</v>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>2026-10-08T14:34:29.961Z</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>2026-10-08 14:35:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B481" s="3" t="n">
+        <v>104.41</v>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>2026-10-08T14:35:24.832Z</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>2026-10-08 14:35:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B482" s="3" t="n">
+        <v>25.87</v>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>2026-10-08T00:01:06.952Z</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>2026-10-08 14:35:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B483" s="3" t="n">
+        <v>85.25</v>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>2026-10-08T00:01:34.625Z</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>2026-10-08 14:35:51</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E483"/>
+  <dimension ref="A1:E487"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -12528,6 +12528,106 @@
         </is>
       </c>
     </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B484" s="3" t="n">
+        <v>20.01</v>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>2026-10-09T14:22:29.540Z</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>2026-10-09 14:22:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B485" s="3" t="n">
+        <v>103.9</v>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>2026-10-09T14:22:25.347Z</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>2026-10-09 14:22:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B486" s="3" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>2026-10-09T00:01:07.724Z</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>2026-10-09 14:22:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B487" s="3" t="n">
+        <v>86.88</v>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>2026-10-09T00:01:34.781Z</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>2026-10-09 14:22:49</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E487"/>
+  <dimension ref="A1:E491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -12628,6 +12628,106 @@
         </is>
       </c>
     </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B488" s="3" t="n">
+        <v>19.964</v>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>2026-10-10T13:39:20.716Z</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>2026-10-10 13:44:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B489" s="3" t="n">
+        <v>104.42</v>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>2026-10-10T13:30:46.462Z</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>2026-10-10 13:44:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B490" s="3" t="n">
+        <v>25.98</v>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>2026-10-10T00:06:05.853Z</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>2026-10-10 13:44:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B491" s="3" t="n">
+        <v>86.94</v>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>2026-10-10T00:06:36.021Z</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>2026-10-10 13:44:24</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E491"/>
+  <dimension ref="A1:E495"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -12728,6 +12728,106 @@
         </is>
       </c>
     </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B492" s="3" t="n">
+        <v>19.96</v>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>2026-10-11T13:33:35.925Z</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>2026-10-11 14:04:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B493" s="3" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>2026-10-11T14:01:16.485Z</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>2026-10-11 14:04:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B494" s="3" t="n">
+        <v>25.98</v>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>2026-10-10T00:06:05.853Z</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>2026-10-11 14:04:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B495" s="3" t="n">
+        <v>86.94</v>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>2026-10-10T00:06:36.021Z</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>2026-10-11 14:04:03</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E495"/>
+  <dimension ref="A1:E499"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -12828,6 +12828,106 @@
         </is>
       </c>
     </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B496" s="3" t="n">
+        <v>210.45</v>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>2026-10-12T16:40:07.372Z</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:44:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B497" s="3" t="n">
+        <v>106.71</v>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>2026-10-12T16:43:09.220Z</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:44:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B498" s="3" t="n">
+        <v>25.98</v>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>2026-10-10T00:06:05.853Z</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:44:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B499" s="3" t="n">
+        <v>86.94</v>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>2026-10-10T00:06:36.021Z</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>2026-10-12 16:44:51</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E499"/>
+  <dimension ref="A1:E503"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -12928,6 +12928,106 @@
         </is>
       </c>
     </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B500" s="3" t="n">
+        <v>215.5</v>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>2026-10-13T14:58:16.885Z</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>2026-10-13 15:04:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B501" s="3" t="n">
+        <v>105.72</v>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>2026-10-13T15:02:36.889Z</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>2026-10-13 15:04:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B502" s="3" t="n">
+        <v>26.09</v>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>2026-10-13T00:01:10.569Z</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>2026-10-13 15:04:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B503" s="3" t="n">
+        <v>88.34</v>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>2026-10-13T00:01:40.904Z</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>2026-10-13 15:04:25</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E503"/>
+  <dimension ref="A1:E507"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -13028,6 +13028,106 @@
         </is>
       </c>
     </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B504" s="3" t="n">
+        <v>211.2</v>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>2026-10-14T12:46:21.326Z</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>2026-10-14 12:53:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B505" s="3" t="n">
+        <v>106.07</v>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>2026-10-14T12:52:33.794Z</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>2026-10-14 12:53:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B506" s="3" t="n">
+        <v>26.27</v>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>2026-10-14T00:05:56.788Z</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>2026-10-14 12:53:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B507" s="3" t="n">
+        <v>88.05</v>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>2026-10-14T00:06:24.223Z</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>2026-10-14 12:53:09</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E507"/>
+  <dimension ref="A1:E511"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -13128,6 +13128,106 @@
         </is>
       </c>
     </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B508" s="3" t="n">
+        <v>211.07</v>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>2026-10-15T12:39:20.099Z</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:39:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B509" s="3" t="n">
+        <v>104.43</v>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>2026-10-15T12:38:40.076Z</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:39:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B510" s="3" t="n">
+        <v>26.39</v>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>2026-10-15T00:06:13.801Z</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:39:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B511" s="3" t="n">
+        <v>87.14</v>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>2026-10-15T00:06:58.439Z</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>2026-10-15 12:39:44</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E511"/>
+  <dimension ref="A1:E515"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -13228,6 +13228,106 @@
         </is>
       </c>
     </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B512" s="3" t="n">
+        <v>217.7</v>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>2026-10-16T12:25:17.001Z</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>2026-10-16 12:26:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B513" s="3" t="n">
+        <v>106.09</v>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>2026-10-16T12:26:30.940Z</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>2026-10-16 12:26:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B514" s="3" t="n">
+        <v>29.34</v>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>2026-10-16T00:01:33.636Z</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>2026-10-16 12:26:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B515" s="3" t="n">
+        <v>85.84</v>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>2026-10-16T00:02:17.736Z</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>2026-10-16 12:26:44</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E515"/>
+  <dimension ref="A1:E519"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -13328,6 +13328,106 @@
         </is>
       </c>
     </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B516" s="3" t="n">
+        <v>218.5</v>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>2026-10-17T11:32:18.622Z</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>2026-10-17 11:37:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B517" s="3" t="n">
+        <v>109.95</v>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>2026-10-17T11:02:56.642Z</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>2026-10-17 11:37:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B518" s="3" t="n">
+        <v>29.93</v>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>2026-10-17T00:01:12.725Z</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>2026-10-17 11:37:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B519" s="3" t="n">
+        <v>85.41</v>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>2026-10-17T00:02:02.344Z</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>2026-10-17 11:37:56</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E519"/>
+  <dimension ref="A1:E523"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -13428,6 +13428,106 @@
         </is>
       </c>
     </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B520" s="3" t="n">
+        <v>216.4</v>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>2026-10-18T11:39:55.188Z</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>2026-10-18 12:03:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B521" s="3" t="n">
+        <v>109.95</v>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>2026-10-18T11:56:21.429Z</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>2026-10-18 12:03:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B522" s="3" t="n">
+        <v>29.93</v>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>2026-10-17T00:01:12.725Z</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>2026-10-18 12:03:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B523" s="3" t="n">
+        <v>85.41</v>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>2026-10-17T00:02:02.344Z</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>2026-10-18 12:03:54</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E523"/>
+  <dimension ref="A1:E527"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -13528,6 +13528,106 @@
         </is>
       </c>
     </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B524" s="3" t="n">
+        <v>217.73</v>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>2026-10-19T14:40:23.131Z</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>2026-10-19 14:41:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B525" s="3" t="n">
+        <v>108.13</v>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>2026-10-19T14:40:18.878Z</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>2026-10-19 14:41:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B526" s="3" t="n">
+        <v>29.93</v>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>2026-10-17T00:01:12.725Z</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>2026-10-19 14:41:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B527" s="3" t="n">
+        <v>85.41</v>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>2026-10-17T00:02:02.344Z</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>2026-10-19 14:41:26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E527"/>
+  <dimension ref="A1:E531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -13628,6 +13628,106 @@
         </is>
       </c>
     </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B528" s="3" t="n">
+        <v>221.97</v>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>2026-10-20T12:40:25.579Z</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:44:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B529" s="3" t="n">
+        <v>111.28</v>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>2026-10-20T12:43:22.677Z</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:44:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B530" s="3" t="n">
+        <v>30.01</v>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>2026-10-20T00:05:52.583Z</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:44:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B531" s="3" t="n">
+        <v>85.40000000000001</v>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>2026-10-20T00:06:17.295Z</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:44:03</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E531"/>
+  <dimension ref="A1:E535"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -13728,6 +13728,106 @@
         </is>
       </c>
     </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B532" s="3" t="n">
+        <v>212.1</v>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>2026-10-21T12:46:36.441Z</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:56:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B533" s="3" t="n">
+        <v>108.68</v>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>2026-10-21T12:56:15.359Z</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:56:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B534" s="3" t="n">
+        <v>29.55</v>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>2026-10-21T00:01:05.760Z</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:56:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B535" s="3" t="n">
+        <v>85.65000000000001</v>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>2026-10-21T00:01:36.663Z</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:56:38</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E535"/>
+  <dimension ref="A1:E539"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -13828,6 +13828,106 @@
         </is>
       </c>
     </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B536" s="3" t="n">
+        <v>222</v>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>2026-10-22T12:58:16.957Z</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:58:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B537" s="3" t="n">
+        <v>111.81</v>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>2026-10-22T12:58:12.705Z</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:58:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B538" s="3" t="n">
+        <v>30.06</v>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:01:06.218Z</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:58:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B539" s="3" t="n">
+        <v>85.91</v>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>2026-10-22T00:01:35.883Z</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:58:48</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E539"/>
+  <dimension ref="A1:E543"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -13928,6 +13928,106 @@
         </is>
       </c>
     </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B540" s="3" t="n">
+        <v>228.2</v>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:34:33.075Z</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:38:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B541" s="3" t="n">
+        <v>114.95</v>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>2026-10-23T12:37:07.368Z</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:38:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B542" s="3" t="n">
+        <v>30.63</v>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:01:08.223Z</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:38:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B543" s="3" t="n">
+        <v>86.47</v>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:01:35.538Z</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>2026-10-23 12:38:07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E543"/>
+  <dimension ref="A1:E547"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -14028,6 +14028,106 @@
         </is>
       </c>
     </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B544" s="3" t="n">
+        <v>230.84</v>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>2026-10-24T11:16:07.193Z</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>2026-10-24 12:00:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B545" s="3" t="n">
+        <v>117.38</v>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>2026-10-24T11:45:53.404Z</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>2026-10-24 12:00:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B546" s="3" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:00:53.514Z</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>2026-10-24 12:00:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B547" s="3" t="n">
+        <v>86.26000000000001</v>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:01:17.610Z</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>2026-10-24 12:00:58</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E547"/>
+  <dimension ref="A1:E551"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -14128,6 +14128,106 @@
         </is>
       </c>
     </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B548" s="3" t="n">
+        <v>230.84</v>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>2026-10-25T12:16:04.325Z</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>2026-10-25 12:34:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B549" s="3" t="n">
+        <v>117.38</v>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>2026-10-25T12:31:12.530Z</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>2026-10-25 12:34:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B550" s="3" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:00:53.514Z</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>2026-10-25 12:34:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B551" s="3" t="n">
+        <v>86.26000000000001</v>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:01:17.610Z</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>2026-10-25 12:34:50</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E551"/>
+  <dimension ref="A1:E555"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -14228,6 +14228,106 @@
         </is>
       </c>
     </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B552" s="3" t="n">
+        <v>236.78</v>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>2026-10-26T14:16:26.694Z</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>2026-10-26 14:17:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B553" s="3" t="n">
+        <v>115.54</v>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>2026-10-26T14:16:11.021Z</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>2026-10-26 14:17:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B554" s="3" t="n">
+        <v>31.42</v>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:00:53.514Z</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>2026-10-26 14:17:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B555" s="3" t="n">
+        <v>86.26000000000001</v>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:01:17.610Z</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>2026-10-26 14:17:46</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E555"/>
+  <dimension ref="A1:E559"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -14328,6 +14328,106 @@
         </is>
       </c>
     </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B556" s="3" t="n">
+        <v>234.4</v>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>2026-10-27T13:10:24.976Z</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>2026-10-27 13:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B557" s="3" t="n">
+        <v>115.09</v>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>2026-10-27T13:11:39.065Z</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>2026-10-27 13:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B558" s="3" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>2026-10-27T00:01:23.565Z</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>2026-10-27 13:13:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B559" s="3" t="n">
+        <v>88.19</v>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>2026-10-27T00:01:53.242Z</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>2026-10-27 13:13:10</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E559"/>
+  <dimension ref="A1:E563"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -14428,6 +14428,106 @@
         </is>
       </c>
     </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B560" s="3" t="n">
+        <v>246.8</v>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>2026-10-28T13:58:24.871Z</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>2026-10-28 14:02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B561" s="3" t="n">
+        <v>115.24</v>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>2026-10-28T14:01:36.821Z</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>2026-10-28 14:02:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B562" s="3" t="n">
+        <v>31.74</v>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>2026-10-28T00:06:25.594Z</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>2026-10-28 14:02:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B563" s="3" t="n">
+        <v>88.05</v>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>2026-10-28T00:07:00.677Z</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>2026-10-28 14:02:15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E563"/>
+  <dimension ref="A1:E567"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -14528,6 +14528,106 @@
         </is>
       </c>
     </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B564" s="3" t="n">
+        <v>241.74</v>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>2026-10-29T14:16:23.388Z</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>2026-10-29 14:22:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B565" s="3" t="n">
+        <v>114.54</v>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>2026-10-29T14:21:20.282Z</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>2026-10-29 14:22:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B566" s="3" t="n">
+        <v>32.35</v>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>2026-10-29T00:01:16.042Z</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>2026-10-29 14:22:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B567" s="3" t="n">
+        <v>89.09999999999999</v>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>2026-10-29T00:01:50.590Z</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>2026-10-29 14:22:07</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E567"/>
+  <dimension ref="A1:E571"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -14628,6 +14628,106 @@
         </is>
       </c>
     </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B568" s="3" t="n">
+        <v>255.6</v>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>2026-10-30T13:46:24.078Z</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>2026-10-30 14:11:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B569" s="3" t="n">
+        <v>115.39</v>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>2026-10-30T14:10:44.005Z</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>2026-10-30 14:11:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B570" s="3" t="n">
+        <v>32.03</v>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>2026-10-30T00:01:04.873Z</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>2026-10-30 14:11:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B571" s="3" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>2026-10-30T00:01:51.701Z</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>2026-10-30 14:11:04</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Historico_OilPrice.xlsx
+++ b/Historico_OilPrice.xlsx
@@ -441,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E571"/>
+  <dimension ref="A1:E575"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -14728,6 +14728,106 @@
         </is>
       </c>
     </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>NATURAL_GAS_GBP</t>
+        </is>
+      </c>
+      <c r="B572" s="3" t="n">
+        <v>255.4</v>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>GBp</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>2026-10-31T12:45:31.226Z</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>2026-10-31 13:39:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>BRENT_CRUDE_USD</t>
+        </is>
+      </c>
+      <c r="B573" s="3" t="n">
+        <v>113.4</v>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>2026-10-31T13:26:50.150Z</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>2026-10-31 13:39:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>JKM_LNG_USD</t>
+        </is>
+      </c>
+      <c r="B574" s="3" t="n">
+        <v>32.84</v>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>2026-10-31T00:35:54.260Z</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>2026-10-31 13:39:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>EU_CARBON_EUR</t>
+        </is>
+      </c>
+      <c r="B575" s="3" t="n">
+        <v>89.19</v>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>2026-10-31T00:36:17.953Z</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>2026-10-31 13:39:43</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
